--- a/baselines/threshold-based-baseline/predicted_X_df_baseline.xlsx
+++ b/baselines/threshold-based-baseline/predicted_X_df_baseline.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B253"/>
+  <dimension ref="A1:B337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,7 +442,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.65</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -472,7 +472,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -482,27 +482,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6.95</v>
+        <v>3.75</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6.95</v>
+        <v>3.75</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9.15</v>
+        <v>6.3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9.25</v>
+        <v>6.3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -522,11 +522,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11.3</v>
+        <v>6.3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -536,43 +536,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13.65</v>
+        <v>11.3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13.65</v>
+        <v>11.3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15.6</v>
+        <v>13.45</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15.7</v>
+        <v>13.45</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -582,37 +582,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>13.45</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>17.7</v>
+        <v>15.45</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18.05</v>
+        <v>15.45</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18.75</v>
+        <v>15.45</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20.1</v>
+        <v>17.45</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -632,87 +632,87 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22.6</v>
+        <v>17.45</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22.65</v>
+        <v>17.45</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>24.75</v>
+        <v>20.1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>25</v>
+        <v>20.1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27.65</v>
+        <v>20.1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>27.65</v>
+        <v>22.8</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>31.55</v>
+        <v>22.8</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>34.35</v>
+        <v>22.8</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>37.9</v>
+        <v>25.95</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -722,57 +722,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>38.15</v>
+        <v>25.95</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>38.65</v>
+        <v>25.95</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>40.1</v>
+        <v>30.1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>40.2</v>
+        <v>30.1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>42.1</v>
+        <v>30.1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>42.3</v>
+        <v>32.45</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>42.3</v>
+        <v>32.45</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>46.25</v>
+        <v>32.45</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -802,97 +802,97 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>46.65</v>
+        <v>34.6</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>47.15</v>
+        <v>34.6</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>49.55</v>
+        <v>34.6</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>49.6</v>
+        <v>36.75</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>50.55</v>
+        <v>36.75</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>51.9</v>
+        <v>36.75</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>52.65</v>
+        <v>38.95</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>53.85</v>
+        <v>38.95</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>53.95</v>
+        <v>38.95</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>54.8</v>
+        <v>41.1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -902,57 +902,57 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>56</v>
+        <v>41.1</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>56.3</v>
+        <v>41.1</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>57</v>
+        <v>43.1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>58.3</v>
+        <v>43.1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>59.75</v>
+        <v>43.1</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>60.4</v>
+        <v>47</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -962,97 +962,97 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>62.55</v>
+        <v>47</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>63.5</v>
+        <v>47</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>63.85</v>
+        <v>49.75</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>64.75</v>
+        <v>49.75</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>66.90000000000001</v>
+        <v>49.75</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>66.90000000000001</v>
+        <v>51.75</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>68.95</v>
+        <v>51.75</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>68.95</v>
+        <v>51.75</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>70.55</v>
+        <v>53.8</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>71.05</v>
+        <v>53.8</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1062,27 +1062,27 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>71.7</v>
+        <v>53.8</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>72.8</v>
+        <v>56.65</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>73.15000000000001</v>
+        <v>56.65</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1092,17 +1092,17 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>73.8</v>
+        <v>56.65</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>80.8</v>
+        <v>61.9</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1112,27 +1112,27 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>83</v>
+        <v>61.9</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>87.84999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>91.34999999999999</v>
+        <v>64.25</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -1142,27 +1142,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>94.05</v>
+        <v>64.25</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>99.95</v>
+        <v>64.25</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>102.1</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>102.1</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>102.65</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>104.95</v>
+        <v>68.95</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>106.3</v>
+        <v>68.95</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>106.55</v>
+        <v>68.95</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>107.7</v>
+        <v>72</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>110.6</v>
+        <v>74.3</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>111.4</v>
+        <v>74.3</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -1272,107 +1272,107 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>114.35</v>
+        <v>74.3</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>114.75</v>
+        <v>76.95</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>114.8</v>
+        <v>76.95</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>116.35</v>
+        <v>76.95</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>116.8</v>
+        <v>79.3</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>116.8</v>
+        <v>79.3</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118.8</v>
+        <v>79.3</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118.8</v>
+        <v>81.45</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>122.25</v>
+        <v>81.45</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>122.25</v>
+        <v>81.45</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124.75</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124.75</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125.3</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126.9</v>
+        <v>89.55</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126.9</v>
+        <v>89.55</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127.35</v>
+        <v>89.55</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -1432,57 +1432,57 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128.9</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129.55</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129.95</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131.1</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132.45</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134</v>
+        <v>98.55</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -1502,87 +1502,87 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>136.05</v>
+        <v>98.55</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>138.35</v>
+        <v>98.55</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>138.75</v>
+        <v>100.9</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>138.75</v>
+        <v>100.9</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>140.4</v>
+        <v>100.9</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>141.35</v>
+        <v>103.3</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>141.45</v>
+        <v>103.3</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>142.4</v>
+        <v>103.3</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>145.55</v>
+        <v>105.7</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>145.85</v>
+        <v>105.7</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -1602,107 +1602,107 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>147.55</v>
+        <v>105.7</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>148.95</v>
+        <v>108.1</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>149.55</v>
+        <v>108.1</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>150.35</v>
+        <v>108.1</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>151.05</v>
+        <v>110.75</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>152.65</v>
+        <v>110.75</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>153.1</v>
+        <v>110.75</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>153.1</v>
+        <v>113.2</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>154.7</v>
+        <v>113.2</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>155.15</v>
+        <v>113.2</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>156.8</v>
+        <v>117.35</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -1712,37 +1712,37 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>156.95</v>
+        <v>117.35</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>157.8</v>
+        <v>117.35</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>158.8</v>
+        <v>119.35</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>160.85</v>
+        <v>119.35</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>160.9</v>
+        <v>119.35</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -1762,27 +1762,27 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>162.85</v>
+        <v>121.8</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>163.15</v>
+        <v>121.8</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>165.05</v>
+        <v>121.8</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -1792,17 +1792,17 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>165.2</v>
+        <v>123.8</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>165.2</v>
+        <v>123.8</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -1812,37 +1812,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>167.1</v>
+        <v>123.8</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>171.2</v>
+        <v>126</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>172.6</v>
+        <v>126</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -1852,57 +1852,57 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>173.2</v>
+        <v>128.3</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>174.15</v>
+        <v>128.3</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>175.05</v>
+        <v>128.3</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>175.2</v>
+        <v>130.85</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>176.25</v>
+        <v>130.85</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>177.3</v>
+        <v>130.85</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -1912,17 +1912,17 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>178.25</v>
+        <v>132.95</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>179.05</v>
+        <v>132.95</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -1932,17 +1932,17 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>179.45</v>
+        <v>132.95</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>180.35</v>
+        <v>136.05</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -1952,37 +1952,37 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>181.25</v>
+        <v>136.05</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>181.8</v>
+        <v>136.05</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>182.4</v>
+        <v>138.9</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>184.4</v>
+        <v>138.9</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>184.4</v>
+        <v>138.9</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -2002,37 +2002,37 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>186.55</v>
+        <v>141.3</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>186.6</v>
+        <v>141.3</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>186.6</v>
+        <v>141.3</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>188.6</v>
+        <v>143.3</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>188.7</v>
+        <v>143.3</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -2052,77 +2052,77 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>191.05</v>
+        <v>143.3</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>191.55</v>
+        <v>145.3</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>192.35</v>
+        <v>145.3</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>197.3</v>
+        <v>145.3</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>197.55</v>
+        <v>147.3</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>200.15</v>
+        <v>147.3</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>200.65</v>
+        <v>147.3</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>203.05</v>
+        <v>150.4</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -2132,57 +2132,57 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>205.15</v>
+        <v>150.4</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>207.05</v>
+        <v>150.4</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>207.05</v>
+        <v>152.5</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>207.2</v>
+        <v>152.5</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>209.45</v>
+        <v>152.5</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>209.45</v>
+        <v>154.5</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -2192,57 +2192,57 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>210.9</v>
+        <v>154.5</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>212.7</v>
+        <v>154.5</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>212.75</v>
+        <v>156.8</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>212.9</v>
+        <v>156.8</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>214.9</v>
+        <v>156.8</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>214.9</v>
+        <v>159.4</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>215.95</v>
+        <v>159.4</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>217.05</v>
+        <v>159.4</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>222.75</v>
+        <v>162</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -2282,97 +2282,97 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>223.4</v>
+        <v>162</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>224.3</v>
+        <v>162</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>226.6</v>
+        <v>166.05</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>226.6</v>
+        <v>166.05</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>228.65</v>
+        <v>166.05</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>229.35</v>
+        <v>168.7</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>229.9</v>
+        <v>168.7</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>230.9</v>
+        <v>168.7</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>231.35</v>
+        <v>171.15</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>233.4</v>
+        <v>171.15</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -2382,17 +2382,17 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>235.75</v>
+        <v>171.15</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>238.05</v>
+        <v>173.9</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -2402,47 +2402,47 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>238.05</v>
+        <v>173.9</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>240.3</v>
+        <v>173.9</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>246.4</v>
+        <v>176.6</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>246.6</v>
+        <v>176.6</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>247.75</v>
+        <v>176.6</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>249.15</v>
+        <v>178.8</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -2462,57 +2462,57 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>254.45</v>
+        <v>178.8</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>254.85</v>
+        <v>178.8</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>256.55</v>
+        <v>182.3</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>258.7</v>
+        <v>182.3</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>259.15</v>
+        <v>182.3</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>259.15</v>
+        <v>184.45</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>261.65</v>
+        <v>184.45</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>261.65</v>
+        <v>184.45</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -2542,17 +2542,17 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>262.3</v>
+        <v>186.95</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>263.65</v>
+        <v>186.95</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -2562,97 +2562,97 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>263.95</v>
+        <v>186.95</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>264.65</v>
+        <v>189.55</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>265.95</v>
+        <v>189.55</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>265.95</v>
+        <v>189.55</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>266.65</v>
+        <v>192.15</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>267.95</v>
+        <v>192.15</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>268.1</v>
+        <v>192.15</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>268.7</v>
+        <v>196</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>269.95</v>
+        <v>196</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>270.25</v>
+        <v>196</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -2662,37 +2662,37 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>271.45</v>
+        <v>198.45</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>272.1</v>
+        <v>198.45</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>272.6</v>
+        <v>198.45</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>274.15</v>
+        <v>200.45</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -2702,77 +2702,77 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>274.3</v>
+        <v>200.45</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>278</v>
+        <v>200.45</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>278.05</v>
+        <v>204.5</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>280</v>
+        <v>204.5</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>280.5</v>
+        <v>204.5</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>280.65</v>
+        <v>207.2</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>282.15</v>
+        <v>207.2</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>284.5</v>
+        <v>207.2</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>284.75</v>
+        <v>209.45</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -2792,107 +2792,107 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>284.75</v>
+        <v>209.45</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>286.6</v>
+        <v>209.45</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>287.25</v>
+        <v>211.5</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>288.7</v>
+        <v>211.5</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>289.15</v>
+        <v>211.5</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>289.25</v>
+        <v>213.8</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>291.25</v>
+        <v>213.8</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>291.35</v>
+        <v>213.8</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>291.35</v>
+        <v>216.3</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>293.3</v>
+        <v>216.3</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>293.35</v>
+        <v>216.3</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>293.35</v>
+        <v>219.3</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -2912,27 +2912,27 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>296.85</v>
+        <v>219.3</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>296.85</v>
+        <v>219.3</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>297.1</v>
+        <v>222.95</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>299.05</v>
+        <v>222.95</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -2952,9 +2952,849 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>299.15</v>
+        <v>222.95</v>
       </c>
       <c r="B253" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>227.65</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>227.65</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>227.65</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>233.4</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>233.4</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>233.4</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>235.7</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>235.7</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>235.7</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>238.15</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>238.15</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>238.15</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>240.3</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>240.3</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>240.3</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>242.55</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>242.55</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>242.55</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>245.95</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>245.95</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>245.95</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>248.4</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>248.4</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>248.4</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>252</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>252</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>252</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>254.45</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>254.45</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>254.45</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>259.15</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>259.15</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>259.15</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>261.2</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>261.2</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>261.2</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>265.95</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>265.95</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>265.95</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>267.95</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>267.95</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>267.95</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>270</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>270</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>270</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>274.9</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>280.6</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>284.45</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>284.45</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>284.45</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>286.6</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>286.6</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>286.6</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>290.5</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>290.5</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>290.5</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>292.75</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>292.75</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>292.75</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>296</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>eID_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>296</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>296</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>298.1</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>eID_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>298.1</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>eID_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>298.1</v>
+      </c>
+      <c r="B337" t="inlineStr">
         <is>
           <t>eID_1</t>
         </is>

--- a/baselines/threshold-based-baseline/predicted_X_df_baseline.xlsx
+++ b/baselines/threshold-based-baseline/predicted_X_df_baseline.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>eID_1</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_1</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>eID_2</t>
+          <t>eID_3</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>eID_3</t>
+          <t>eID_2</t>
         </is>
       </c>
     </row>
